--- a/Dziennik_inwestora.xlsx
+++ b/Dziennik_inwestora.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="v2 (Instytucjonalna)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pozycje otwarte" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,76 +413,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A15:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Current Price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Current Value</t>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data aktualizacji</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cena bieżąca</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="G16" t="n">
         <v>405.2099914550781</v>
       </c>
-      <c r="C2" t="n">
-        <v>405.2099914550781</v>
-      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="G17" t="n">
         <v>402.6199951171875</v>
       </c>
-      <c r="C3" t="n">
-        <v>402.6199951171875</v>
-      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="G24" t="n">
         <v>445.2699890136719</v>
       </c>
-      <c r="C4" t="n">
-        <v>22263.49945068359</v>
-      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>BTC/USDT</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>79395.99000000001</v>
-      </c>
-      <c r="C5" t="n">
-        <v>158791.98</v>
+      <c r="G25" t="n">
+        <v>79745.71000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Dziennik_inwestora.xlsx
+++ b/Dziennik_inwestora.xlsx
@@ -2969,7 +2969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="37" min="1" max="1"/>
@@ -3218,6 +3218,30 @@
       <c r="L10" s="19">
         <f>IF(K10="","",K10/$E$5-1)</f>
         <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Automatyczny Update</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>101521.98</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>2376926.73</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>18155263.37482177</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="37"/>
@@ -4711,7 +4735,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
@@ -4736,7 +4760,7 @@
         <v>410.2</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>409.8399963378906</v>
+        <v>421.9200134277344</v>
       </c>
       <c r="H16" s="22">
         <f>IF(D16="Long", (G16-F16)/F16, IF(D16="Short", (F16-G16)/F16, ""))</f>
@@ -4751,7 +4775,7 @@
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
@@ -4776,7 +4800,7 @@
         <v>396.51</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>397.6000061035156</v>
+        <v>396.7799987792969</v>
       </c>
       <c r="H17" s="22">
         <f>IF(D17="Long", (G17-F17)/F17, IF(D17="Short", (F17-G17)/F17, ""))</f>
@@ -5019,7 +5043,7 @@
     <row r="24" ht="15.75" customHeight="1" s="37">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
@@ -5044,7 +5068,7 @@
         <v>411.99</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>444.6099853515625</v>
+        <v>422.239990234375</v>
       </c>
       <c r="H24" s="22">
         <f>IF(D24="Long", (G24-F24)/F24, IF(D24="Short", (F24-G24)/F24, ""))</f>
@@ -5059,7 +5083,7 @@
     <row r="25" ht="15.75" customHeight="1" s="37">
       <c r="A25" s="21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B25" s="29" t="inlineStr">
@@ -5084,7 +5108,7 @@
         <v>79463</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>81070.42999999999</v>
+        <v>77889.49000000001</v>
       </c>
       <c r="H25" s="22">
         <f>IF(D25="Long", (G25-F25)/F25, IF(D25="Short", (F25-G25)/F25, ""))</f>
@@ -6187,114 +6211,394 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>425.695</v>
+      </c>
       <c r="H5" s="18" t="n"/>
-      <c r="I5" s="18" t="n"/>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n"/>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>412.171</v>
+      </c>
       <c r="H6" s="18" t="n"/>
-      <c r="I6" s="18" t="n"/>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>GOOGL Jul</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>4.695</v>
+      </c>
       <c r="H7" s="18" t="n"/>
-      <c r="I7" s="18" t="n"/>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>V Jun12'26</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>2.445</v>
+      </c>
       <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>US-T GOVT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>99.94634499999999</v>
+      </c>
       <c r="H9" s="18" t="n"/>
-      <c r="I9" s="18" t="n"/>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>AAPL CORP</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>131</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>100.22134</v>
+      </c>
       <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n"/>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>JNJ Jun1'2</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>2.125</v>
+      </c>
       <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n"/>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>AMZN Jun1</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>3.245</v>
+      </c>
       <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>MSFT Jun1</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>14.519</v>
+      </c>
       <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>396.836</v>
+      </c>
       <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Current portfolio entry in a simulated trading environment.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
@@ -7448,7 +7752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25" customWidth="1" style="37" min="1" max="1"/>
@@ -7536,6 +7840,28 @@
       <c r="B7" s="36" t="n"/>
       <c r="C7" s="36" t="n"/>
       <c r="D7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Automatyczne Podsumowanie</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Podstawowe pozycje akcyjne oraz strategie dywidendowe skutecznie budowały bazę portfela, zapewniając stabilność i potencjalny wzrost kapitału. Instrumenty dłużne i lokaty cyfrowe efektywnie pełniły rolę ochronną i dywersyfikacyjną, stabilizując ogólną wartość portfela.</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Segment aktywnego tradingu oraz pozycji lewarowanych, w szczególności ekspozycja na BTC/USDT z wysoką dźwignią, generuje podwyższone ryzyko i wymaga natychmiastowej rewizji. Strategie opcyjne typu 'maszynka ubezpieczeniowa' wymagają bacznego monitorowania pod kątem potencjalnego przejęcia aktywów i zarządzania ryzykiem.</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Konieczne jest ograniczenie ekspozycji na pozycje wysokolewarowane oraz przemyślenie roli aktywnego tradingu w kontekście ogólnego profilu ryzyka portfela. Należy również dokonać przeglądu strategii opcyjnych, aby upewnić się, że są one zgodne z apetytem na ryzyko i celami portfela.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="37"/>
     <row r="22" ht="15.75" customHeight="1" s="37"/>
